--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537868839</v>
+        <v>46157.93111263085</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111263085</v>
+        <v>46157.9336661937</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9336661937</v>
+        <v>46157.93669035378</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93669035378</v>
+        <v>46158.28192934582</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192934582</v>
+        <v>46158.29715183125</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29715183125</v>
+        <v>46158.2978848211</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2978848211</v>
+        <v>46158.33354417133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354417133</v>
+        <v>46158.37209839534</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209839534</v>
+        <v>46158.37266976463</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
